--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120375394</v>
+        <v>120375781</v>
       </c>
       <c r="B2" t="n">
         <v>91881</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537091</v>
+        <v>537122</v>
       </c>
       <c r="R2" t="n">
-        <v>6439460</v>
+        <v>6439387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120375071</v>
+        <v>120379556</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>74593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537126</v>
+        <v>537015</v>
       </c>
       <c r="R3" t="n">
-        <v>6439407</v>
+        <v>6439520</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120390295</v>
+        <v>120374870</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,47 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537052</v>
+        <v>537094</v>
       </c>
       <c r="R4" t="n">
-        <v>6439544</v>
+        <v>6439477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,14 +952,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>vid basen av brant</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,19 +973,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1108,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120390305</v>
+        <v>120374719</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,47 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537033</v>
+        <v>537088</v>
       </c>
       <c r="R6" t="n">
-        <v>6439525</v>
+        <v>6439432</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,29 +1177,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120390059</v>
+        <v>120375204</v>
       </c>
       <c r="B7" t="n">
-        <v>108811</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,38 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537051</v>
+        <v>537127</v>
       </c>
       <c r="R7" t="n">
-        <v>6439570</v>
+        <v>6439407</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,29 +1279,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120390040</v>
+        <v>120379558</v>
       </c>
       <c r="B8" t="n">
-        <v>87348</v>
+        <v>89981</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,45 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4377</v>
+        <v>5685</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537043</v>
+        <v>537031</v>
       </c>
       <c r="R8" t="n">
-        <v>6439682</v>
+        <v>6439570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,29 +1381,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck, Gunilla Rech</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120379556</v>
+        <v>120374873</v>
       </c>
       <c r="B9" t="n">
-        <v>74593</v>
+        <v>91901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,38 +1411,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>5448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537015</v>
+        <v>537033</v>
       </c>
       <c r="R9" t="n">
-        <v>6439520</v>
+        <v>6439605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,9 +1486,24 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gran blandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,22 +1518,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120377550</v>
+        <v>120379933</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>5169</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,38 +1542,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537101</v>
+        <v>537011</v>
       </c>
       <c r="R10" t="n">
-        <v>6439502</v>
+        <v>6439483</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,19 +1620,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:08</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,28 +1636,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120376738</v>
+        <v>120376327</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>8421</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,38 +1667,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537025</v>
+        <v>536994</v>
       </c>
       <c r="R11" t="n">
-        <v>6439477</v>
+        <v>6439456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,9 +1728,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,12 +1755,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1878,10 +1888,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120374719</v>
+        <v>120386436</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
+        <v>4772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,38 +1900,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537088</v>
+        <v>537025</v>
       </c>
       <c r="R13" t="n">
-        <v>6439432</v>
+        <v>6439508</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,22 +1978,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120379933</v>
+        <v>120377550</v>
       </c>
       <c r="B14" t="n">
-        <v>5169</v>
+        <v>91881</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,55 +2002,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537011</v>
+        <v>537101</v>
       </c>
       <c r="R14" t="n">
-        <v>6439483</v>
+        <v>6439502</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,14 +2063,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,29 +2084,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120375781</v>
+        <v>120390290</v>
       </c>
       <c r="B15" t="n">
-        <v>91881</v>
+        <v>4772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2117,38 +2114,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537122</v>
+        <v>537047</v>
       </c>
       <c r="R15" t="n">
-        <v>6439387</v>
+        <v>6439540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,34 +2189,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>gammal gran i brant sluttning</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120386436</v>
+        <v>120376738</v>
       </c>
       <c r="B16" t="n">
-        <v>4772</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2219,38 +2231,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Svartgölen, Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>537025</v>
       </c>
       <c r="R16" t="n">
-        <v>6439508</v>
+        <v>6439477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,22 +2309,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120374870</v>
+        <v>120379559</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>94422</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,38 +2333,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>2671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537094</v>
+        <v>537007</v>
       </c>
       <c r="R17" t="n">
-        <v>6439477</v>
+        <v>6439489</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,19 +2394,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,22 +2411,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120374873</v>
+        <v>120390295</v>
       </c>
       <c r="B18" t="n">
-        <v>91901</v>
+        <v>4772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2433,52 +2435,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5448</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537033</v>
+        <v>537052</v>
       </c>
       <c r="R18" t="n">
-        <v>6439605</v>
+        <v>6439544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,24 +2505,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gran blandskog</t>
+          <t>vid basen av brant</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,25 +2521,26 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120375204</v>
+        <v>120375071</v>
       </c>
       <c r="B19" t="n">
         <v>91881</v>
@@ -2592,7 +2580,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537127</v>
+        <v>537126</v>
       </c>
       <c r="R19" t="n">
         <v>6439407</v>
@@ -2654,10 +2642,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120379559</v>
+        <v>120389940</v>
       </c>
       <c r="B20" t="n">
-        <v>94422</v>
+        <v>91901</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2666,38 +2654,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2671</v>
+        <v>5448</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537007</v>
+        <v>537043</v>
       </c>
       <c r="R20" t="n">
-        <v>6439489</v>
+        <v>6439607</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,34 +2731,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>under gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120390290</v>
+        <v>120386440</v>
       </c>
       <c r="B21" t="n">
-        <v>4772</v>
+        <v>100194</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,43 +2777,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537047</v>
+        <v>537030</v>
       </c>
       <c r="R21" t="n">
-        <v>6439540</v>
+        <v>6439597</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,40 +2839,34 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>gammal gran i brant sluttning</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120379558</v>
+        <v>120390059</v>
       </c>
       <c r="B22" t="n">
-        <v>89981</v>
+        <v>108811</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2885,35 +2875,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5685</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537031</v>
+        <v>537051</v>
       </c>
       <c r="R22" t="n">
         <v>6439570</v>
@@ -2957,28 +2951,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120379561</v>
+        <v>120390305</v>
       </c>
       <c r="B23" t="n">
-        <v>100194</v>
+        <v>5169</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2991,34 +2986,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537004</v>
+        <v>537033</v>
       </c>
       <c r="R23" t="n">
-        <v>6439579</v>
+        <v>6439525</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,28 +3063,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120386440</v>
+        <v>120375394</v>
       </c>
       <c r="B24" t="n">
-        <v>100194</v>
+        <v>91881</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3089,38 +3094,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537030</v>
+        <v>537091</v>
       </c>
       <c r="R24" t="n">
-        <v>6439597</v>
+        <v>6439460</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,9 +3155,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,22 +3182,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120389940</v>
+        <v>120390040</v>
       </c>
       <c r="B25" t="n">
-        <v>91901</v>
+        <v>87348</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,25 +3206,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5448</v>
+        <v>4377</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blodvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3233,7 +3248,7 @@
         <v>537043</v>
       </c>
       <c r="R25" t="n">
-        <v>6439607</v>
+        <v>6439682</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3266,11 +3281,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>under gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,10 +3308,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120376327</v>
+        <v>120379561</v>
       </c>
       <c r="B26" t="n">
-        <v>8421</v>
+        <v>100194</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3314,21 +3324,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3338,10 +3348,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536994</v>
+        <v>537004</v>
       </c>
       <c r="R26" t="n">
-        <v>6439456</v>
+        <v>6439579</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3371,19 +3381,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,15 +3398,224 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120411279</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svartgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>537083</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6439499</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>8 ex</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120411281</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svartgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>537105</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6439457</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120374873</v>
+        <v>120379933</v>
       </c>
       <c r="B9" t="n">
-        <v>91901</v>
+        <v>5169</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5448</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1439,24 +1439,27 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537033</v>
+        <v>537011</v>
       </c>
       <c r="R9" t="n">
-        <v>6439605</v>
+        <v>6439483</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,24 +1489,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gran blandskog</t>
+          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,28 +1505,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120379933</v>
+        <v>120379555</v>
       </c>
       <c r="B10" t="n">
-        <v>5169</v>
+        <v>74466</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,51 +1540,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6428</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537011</v>
+        <v>537027</v>
       </c>
       <c r="R10" t="n">
-        <v>6439483</v>
+        <v>6439571</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,11 +1605,6 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1640,25 +1615,40 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120376327</v>
+        <v>120374873</v>
       </c>
       <c r="B11" t="n">
-        <v>8421</v>
+        <v>91901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,38 +1657,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>5448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536994</v>
+        <v>537033</v>
       </c>
       <c r="R11" t="n">
-        <v>6439456</v>
+        <v>6439605</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1744,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gran blandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,22 +1764,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120379555</v>
+        <v>120376327</v>
       </c>
       <c r="B12" t="n">
-        <v>74466</v>
+        <v>8421</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,37 +1792,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537027</v>
+        <v>536994</v>
       </c>
       <c r="R12" t="n">
-        <v>6439571</v>
+        <v>6439456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,45 +1849,39 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120379559</v>
+        <v>120390295</v>
       </c>
       <c r="B17" t="n">
-        <v>94422</v>
+        <v>4772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,34 +2337,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2671</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537007</v>
+        <v>537052</v>
       </c>
       <c r="R17" t="n">
-        <v>6439489</v>
+        <v>6439544</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,34 +2408,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>vid basen av brant</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120390295</v>
+        <v>120379559</v>
       </c>
       <c r="B18" t="n">
-        <v>4772</v>
+        <v>94422</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,43 +2454,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>2671</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537052</v>
+        <v>537007</v>
       </c>
       <c r="R18" t="n">
-        <v>6439544</v>
+        <v>6439489</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,30 +2516,24 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>vid basen av brant</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120390040</v>
+        <v>120379561</v>
       </c>
       <c r="B25" t="n">
-        <v>87348</v>
+        <v>100194</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3210,45 +3210,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4377</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537043</v>
+        <v>537004</v>
       </c>
       <c r="R25" t="n">
-        <v>6439682</v>
+        <v>6439579</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3289,29 +3278,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120379561</v>
+        <v>120390040</v>
       </c>
       <c r="B26" t="n">
-        <v>100194</v>
+        <v>87348</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3324,34 +3312,45 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>4377</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blodvaxskivling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537004</v>
+        <v>537043</v>
       </c>
       <c r="R26" t="n">
-        <v>6439579</v>
+        <v>6439682</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,18 +3391,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120375781</v>
+        <v>120386440</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537122</v>
+        <v>537030</v>
       </c>
       <c r="R2" t="n">
-        <v>6439387</v>
+        <v>6439597</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120379556</v>
+        <v>120390059</v>
       </c>
       <c r="B3" t="n">
-        <v>74593</v>
+        <v>108811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537015</v>
+        <v>537051</v>
       </c>
       <c r="R3" t="n">
-        <v>6439520</v>
+        <v>6439570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,25 +865,26 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120374870</v>
+        <v>120375204</v>
       </c>
       <c r="B4" t="n">
         <v>91881</v>
@@ -915,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537094</v>
+        <v>537127</v>
       </c>
       <c r="R4" t="n">
-        <v>6439477</v>
+        <v>6439407</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +957,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120379560</v>
+        <v>120390290</v>
       </c>
       <c r="B5" t="n">
-        <v>100194</v>
+        <v>4772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1002,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537001</v>
+        <v>537047</v>
       </c>
       <c r="R5" t="n">
-        <v>6439528</v>
+        <v>6439540</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,34 +1073,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>gammal gran i brant sluttning</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120374719</v>
+        <v>120379559</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>94422</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,38 +1115,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537088</v>
+        <v>537007</v>
       </c>
       <c r="R6" t="n">
-        <v>6439432</v>
+        <v>6439489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,22 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120375204</v>
+        <v>120386436</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>4772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537127</v>
+        <v>537025</v>
       </c>
       <c r="R7" t="n">
-        <v>6439407</v>
+        <v>6439508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120379558</v>
+        <v>120379933</v>
       </c>
       <c r="B8" t="n">
-        <v>89981</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,34 +1323,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5685</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537031</v>
+        <v>537011</v>
       </c>
       <c r="R8" t="n">
-        <v>6439570</v>
+        <v>6439483</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,34 +1402,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Gunilla Rech</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120379933</v>
+        <v>120390040</v>
       </c>
       <c r="B9" t="n">
-        <v>5169</v>
+        <v>87348</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1448,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>4377</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blodvaxskivling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1439,27 +1472,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537011</v>
+        <v>537043</v>
       </c>
       <c r="R9" t="n">
-        <v>6439483</v>
+        <v>6439682</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,11 +1521,6 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1512,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120379555</v>
+        <v>120379556</v>
       </c>
       <c r="B10" t="n">
-        <v>74466</v>
+        <v>74593</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,37 +1562,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6428</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537027</v>
+        <v>537015</v>
       </c>
       <c r="R10" t="n">
-        <v>6439571</v>
+        <v>6439520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,24 +1630,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1645,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120374873</v>
+        <v>120375071</v>
       </c>
       <c r="B11" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,48 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537033</v>
+        <v>537126</v>
       </c>
       <c r="R11" t="n">
-        <v>6439605</v>
+        <v>6439407</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,24 +1721,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gran blandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,22 +1738,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120376327</v>
+        <v>120390295</v>
       </c>
       <c r="B12" t="n">
-        <v>8421</v>
+        <v>4772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,34 +1766,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536994</v>
+        <v>537052</v>
       </c>
       <c r="R12" t="n">
-        <v>6439456</v>
+        <v>6439544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,19 +1832,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:10</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>vid basen av brant</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,28 +1848,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120386436</v>
+        <v>120374870</v>
       </c>
       <c r="B13" t="n">
-        <v>4772</v>
+        <v>91881</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1900,38 +1879,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537025</v>
+        <v>537094</v>
       </c>
       <c r="R13" t="n">
-        <v>6439508</v>
+        <v>6439477</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,9 +1940,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1978,22 +1967,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120377550</v>
+        <v>120379558</v>
       </c>
       <c r="B14" t="n">
-        <v>91881</v>
+        <v>89981</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2002,38 +1991,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537101</v>
+        <v>537031</v>
       </c>
       <c r="R14" t="n">
-        <v>6439502</v>
+        <v>6439570</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,19 +2052,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,22 +2069,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jon Liljebäck, Gunilla Rech</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120390290</v>
+        <v>120379555</v>
       </c>
       <c r="B15" t="n">
-        <v>4772</v>
+        <v>74466</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,43 +2097,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>6428</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537047</v>
+        <v>537027</v>
       </c>
       <c r="R15" t="n">
-        <v>6439540</v>
+        <v>6439571</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,11 +2162,6 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>gammal gran i brant sluttning</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2204,25 +2172,40 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120376738</v>
+        <v>120375394</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>91881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,34 +2218,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537025</v>
+        <v>537091</v>
       </c>
       <c r="R16" t="n">
-        <v>6439477</v>
+        <v>6439460</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,9 +2275,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2309,22 +2302,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120390295</v>
+        <v>120379560</v>
       </c>
       <c r="B17" t="n">
-        <v>4772</v>
+        <v>100194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,43 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537052</v>
+        <v>537001</v>
       </c>
       <c r="R17" t="n">
-        <v>6439544</v>
+        <v>6439528</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,40 +2392,34 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>vid basen av brant</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120379559</v>
+        <v>120377550</v>
       </c>
       <c r="B18" t="n">
-        <v>94422</v>
+        <v>91881</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2450,38 +2428,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2671</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537007</v>
+        <v>537101</v>
       </c>
       <c r="R18" t="n">
-        <v>6439489</v>
+        <v>6439502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,9 +2489,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,19 +2516,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120375071</v>
+        <v>120374719</v>
       </c>
       <c r="B19" t="n">
         <v>91881</v>
@@ -2580,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537126</v>
+        <v>537088</v>
       </c>
       <c r="R19" t="n">
-        <v>6439407</v>
+        <v>6439432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2642,10 +2630,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120389940</v>
+        <v>120375781</v>
       </c>
       <c r="B20" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2658,45 +2646,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537043</v>
+        <v>537122</v>
       </c>
       <c r="R20" t="n">
-        <v>6439607</v>
+        <v>6439387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,37 +2708,31 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>under gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120386440</v>
+        <v>120379561</v>
       </c>
       <c r="B21" t="n">
         <v>100194</v>
@@ -2801,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537030</v>
+        <v>537004</v>
       </c>
       <c r="R21" t="n">
-        <v>6439597</v>
+        <v>6439579</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,22 +2822,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120390059</v>
+        <v>120376327</v>
       </c>
       <c r="B22" t="n">
-        <v>108811</v>
+        <v>8421</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2875,42 +2846,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537051</v>
+        <v>536994</v>
       </c>
       <c r="R22" t="n">
-        <v>6439570</v>
+        <v>6439456</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2940,40 +2907,49 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120390305</v>
+        <v>120376738</v>
       </c>
       <c r="B23" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2982,47 +2958,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537033</v>
+        <v>537025</v>
       </c>
       <c r="R23" t="n">
-        <v>6439525</v>
+        <v>6439477</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,29 +3030,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120375394</v>
+        <v>120390305</v>
       </c>
       <c r="B24" t="n">
-        <v>91881</v>
+        <v>5169</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3094,38 +3060,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537091</v>
+        <v>537033</v>
       </c>
       <c r="R24" t="n">
-        <v>6439460</v>
+        <v>6439525</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3155,49 +3130,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120379561</v>
+        <v>120374873</v>
       </c>
       <c r="B25" t="n">
-        <v>100194</v>
+        <v>91901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3206,38 +3172,52 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5448</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537004</v>
+        <v>537033</v>
       </c>
       <c r="R25" t="n">
-        <v>6439579</v>
+        <v>6439605</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3267,9 +3247,24 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gran blandskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,22 +3279,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120390040</v>
+        <v>120389940</v>
       </c>
       <c r="B26" t="n">
-        <v>87348</v>
+        <v>91901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3308,25 +3303,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4377</v>
+        <v>5448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3350,7 +3345,7 @@
         <v>537043</v>
       </c>
       <c r="R26" t="n">
-        <v>6439682</v>
+        <v>6439607</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3383,6 +3378,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>under gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3410,7 +3410,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120411279</v>
+        <v>120411281</v>
       </c>
       <c r="B27" t="n">
         <v>91881</v>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537083</v>
+        <v>537105</v>
       </c>
       <c r="R27" t="n">
-        <v>6439499</v>
+        <v>6439457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,11 +3486,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3517,7 +3512,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120411281</v>
+        <v>120411279</v>
       </c>
       <c r="B28" t="n">
         <v>91881</v>
@@ -3557,10 +3552,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537105</v>
+        <v>537083</v>
       </c>
       <c r="R28" t="n">
-        <v>6439457</v>
+        <v>6439499</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3593,6 +3588,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120375071</v>
+        <v>120390295</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>4772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,38 +1660,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537126</v>
+        <v>537052</v>
       </c>
       <c r="R11" t="n">
-        <v>6439407</v>
+        <v>6439544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,34 +1735,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>vid basen av brant</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120390295</v>
+        <v>120375071</v>
       </c>
       <c r="B12" t="n">
-        <v>4772</v>
+        <v>91881</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,47 +1777,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537052</v>
+        <v>537126</v>
       </c>
       <c r="R12" t="n">
-        <v>6439544</v>
+        <v>6439407</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,30 +1843,24 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>vid basen av brant</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120379561</v>
+        <v>120376327</v>
       </c>
       <c r="B21" t="n">
-        <v>100194</v>
+        <v>8421</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537004</v>
+        <v>536994</v>
       </c>
       <c r="R21" t="n">
-        <v>6439579</v>
+        <v>6439456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,9 +2805,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2822,22 +2832,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120376327</v>
+        <v>120379561</v>
       </c>
       <c r="B22" t="n">
-        <v>8421</v>
+        <v>100194</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2850,21 +2860,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2874,10 +2884,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536994</v>
+        <v>537004</v>
       </c>
       <c r="R22" t="n">
-        <v>6439456</v>
+        <v>6439579</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,19 +2917,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2934,12 +2934,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120386440</v>
+        <v>120379555</v>
       </c>
       <c r="B2" t="n">
-        <v>100194</v>
+        <v>74466</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537030</v>
+        <v>537027</v>
       </c>
       <c r="R2" t="n">
-        <v>6439597</v>
+        <v>6439571</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,28 +762,44 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120390059</v>
+        <v>120386436</v>
       </c>
       <c r="B3" t="n">
-        <v>108811</v>
+        <v>4772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537051</v>
+        <v>537025</v>
       </c>
       <c r="R3" t="n">
-        <v>6439570</v>
+        <v>6439508</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,26 +880,25 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120375204</v>
+        <v>120377550</v>
       </c>
       <c r="B4" t="n">
         <v>91881</v>
@@ -920,14 +934,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537127</v>
+        <v>537101</v>
       </c>
       <c r="R4" t="n">
-        <v>6439407</v>
+        <v>6439502</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,9 +971,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +998,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120390290</v>
+        <v>120376738</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,47 +1022,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537047</v>
+        <v>537025</v>
       </c>
       <c r="R5" t="n">
-        <v>6439540</v>
+        <v>6439477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,40 +1088,34 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>gammal gran i brant sluttning</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120379559</v>
+        <v>120379558</v>
       </c>
       <c r="B6" t="n">
-        <v>94422</v>
+        <v>89981</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537007</v>
+        <v>537031</v>
       </c>
       <c r="R6" t="n">
-        <v>6439489</v>
+        <v>6439570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,14 +1207,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Jon Liljebäck, Gunilla Rech</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120386436</v>
+        <v>120390290</v>
       </c>
       <c r="B7" t="n">
         <v>4772</v>
@@ -1239,16 +1248,25 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537025</v>
+        <v>537047</v>
       </c>
       <c r="R7" t="n">
-        <v>6439508</v>
+        <v>6439540</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,34 +1301,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>gammal gran i brant sluttning</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120379933</v>
+        <v>120389940</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
+        <v>91901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1343,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1347,27 +1371,21 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537011</v>
+        <v>537043</v>
       </c>
       <c r="R8" t="n">
-        <v>6439483</v>
+        <v>6439607</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1422,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
+          <t>under gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,22 +1438,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120390040</v>
+        <v>120379933</v>
       </c>
       <c r="B9" t="n">
-        <v>87348</v>
+        <v>5169</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,21 +1466,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4377</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1472,21 +1490,27 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537043</v>
+        <v>537011</v>
       </c>
       <c r="R9" t="n">
-        <v>6439682</v>
+        <v>6439483</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,6 +1545,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1534,22 +1563,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120379556</v>
+        <v>120379560</v>
       </c>
       <c r="B10" t="n">
-        <v>74593</v>
+        <v>100194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537015</v>
+        <v>537001</v>
       </c>
       <c r="R10" t="n">
-        <v>6439520</v>
+        <v>6439528</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120390295</v>
+        <v>120379556</v>
       </c>
       <c r="B11" t="n">
-        <v>4772</v>
+        <v>74593</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,43 +1693,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537052</v>
+        <v>537015</v>
       </c>
       <c r="R11" t="n">
-        <v>6439544</v>
+        <v>6439520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,40 +1755,34 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>vid basen av brant</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120375071</v>
+        <v>120376327</v>
       </c>
       <c r="B12" t="n">
-        <v>91881</v>
+        <v>8421</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,38 +1791,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537126</v>
+        <v>536994</v>
       </c>
       <c r="R12" t="n">
-        <v>6439407</v>
+        <v>6439456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,9 +1852,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,22 +1879,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120374870</v>
+        <v>120390059</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
+        <v>108811</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,34 +1907,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537094</v>
+        <v>537051</v>
       </c>
       <c r="R13" t="n">
-        <v>6439477</v>
+        <v>6439570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,49 +1968,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120379558</v>
+        <v>120379559</v>
       </c>
       <c r="B14" t="n">
-        <v>89981</v>
+        <v>94422</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5685</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537031</v>
+        <v>537007</v>
       </c>
       <c r="R14" t="n">
-        <v>6439570</v>
+        <v>6439489</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,17 +2093,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Gunilla Rech</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120379555</v>
+        <v>120379561</v>
       </c>
       <c r="B15" t="n">
-        <v>74466</v>
+        <v>100194</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,37 +2116,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6428</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537027</v>
+        <v>537004</v>
       </c>
       <c r="R15" t="n">
-        <v>6439571</v>
+        <v>6439579</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,24 +2184,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120375394</v>
+        <v>120390295</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>4772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,38 +2214,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537091</v>
+        <v>537052</v>
       </c>
       <c r="R16" t="n">
-        <v>6439460</v>
+        <v>6439544</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,19 +2284,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:31</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>vid basen av brant</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2296,25 +2300,26 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120379560</v>
+        <v>120386440</v>
       </c>
       <c r="B17" t="n">
         <v>100194</v>
@@ -2354,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537001</v>
+        <v>537030</v>
       </c>
       <c r="R17" t="n">
-        <v>6439528</v>
+        <v>6439597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2404,19 +2409,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120377550</v>
+        <v>120375394</v>
       </c>
       <c r="B18" t="n">
         <v>91881</v>
@@ -2452,14 +2457,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537101</v>
+        <v>537091</v>
       </c>
       <c r="R18" t="n">
-        <v>6439502</v>
+        <v>6439460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2501,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,12 +2521,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2630,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120375781</v>
+        <v>120390305</v>
       </c>
       <c r="B20" t="n">
-        <v>91881</v>
+        <v>5169</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2642,38 +2647,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537122</v>
+        <v>537033</v>
       </c>
       <c r="R20" t="n">
-        <v>6439387</v>
+        <v>6439525</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,28 +2728,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120376327</v>
+        <v>120375781</v>
       </c>
       <c r="B21" t="n">
-        <v>8421</v>
+        <v>91881</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,38 +2759,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536994</v>
+        <v>537122</v>
       </c>
       <c r="R21" t="n">
-        <v>6439456</v>
+        <v>6439387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,19 +2820,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2832,22 +2837,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120379561</v>
+        <v>120375071</v>
       </c>
       <c r="B22" t="n">
-        <v>100194</v>
+        <v>91881</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2856,38 +2861,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537004</v>
+        <v>537126</v>
       </c>
       <c r="R22" t="n">
-        <v>6439579</v>
+        <v>6439407</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,22 +2939,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120376738</v>
+        <v>120390040</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>87348</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2958,38 +2963,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>4377</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537025</v>
+        <v>537043</v>
       </c>
       <c r="R23" t="n">
-        <v>6439477</v>
+        <v>6439682</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,28 +3046,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120390305</v>
+        <v>120374873</v>
       </c>
       <c r="B24" t="n">
-        <v>5169</v>
+        <v>91901</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3060,47 +3077,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>5448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
         <v>537033</v>
       </c>
       <c r="R24" t="n">
-        <v>6439525</v>
+        <v>6439605</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,40 +3152,54 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gran blandskog</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120374873</v>
+        <v>120375204</v>
       </c>
       <c r="B25" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3176,48 +3212,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537033</v>
+        <v>537127</v>
       </c>
       <c r="R25" t="n">
-        <v>6439605</v>
+        <v>6439407</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,24 +3269,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gran blandskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3279,22 +3286,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120389940</v>
+        <v>120374870</v>
       </c>
       <c r="B26" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3307,45 +3314,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537043</v>
+        <v>537094</v>
       </c>
       <c r="R26" t="n">
-        <v>6439607</v>
+        <v>6439477</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,14 +3371,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>under gran</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,19 +3392,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120379555</v>
+        <v>120374873</v>
       </c>
       <c r="B2" t="n">
-        <v>74466</v>
+        <v>91901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>5448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537027</v>
+        <v>537033</v>
       </c>
       <c r="R2" t="n">
-        <v>6439571</v>
+        <v>6439605</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,55 +762,54 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gran blandskog</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120386436</v>
+        <v>120374870</v>
       </c>
       <c r="B3" t="n">
-        <v>4772</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +818,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537025</v>
+        <v>537094</v>
       </c>
       <c r="R3" t="n">
-        <v>6439508</v>
+        <v>6439477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,9 +879,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,22 +906,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120377550</v>
+        <v>120390295</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>4772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,38 +930,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537101</v>
+        <v>537052</v>
       </c>
       <c r="R4" t="n">
-        <v>6439502</v>
+        <v>6439544</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,19 +1000,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:08</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>vid basen av brant</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,28 +1016,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120376738</v>
+        <v>120390290</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>4772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,38 +1047,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537025</v>
+        <v>537047</v>
       </c>
       <c r="R5" t="n">
-        <v>6439477</v>
+        <v>6439540</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,34 +1122,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>gammal gran i brant sluttning</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120379558</v>
+        <v>120379560</v>
       </c>
       <c r="B6" t="n">
-        <v>89981</v>
+        <v>100194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,21 +1168,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537031</v>
+        <v>537001</v>
       </c>
       <c r="R6" t="n">
-        <v>6439570</v>
+        <v>6439528</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,14 +1247,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Gunilla Rech</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120390290</v>
+        <v>120386436</v>
       </c>
       <c r="B7" t="n">
         <v>4772</v>
@@ -1248,25 +1288,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537047</v>
+        <v>537025</v>
       </c>
       <c r="R7" t="n">
-        <v>6439540</v>
+        <v>6439508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,30 +1332,24 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>gammal gran i brant sluttning</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1450,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120379933</v>
+        <v>120386440</v>
       </c>
       <c r="B9" t="n">
-        <v>5169</v>
+        <v>100194</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,51 +1491,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537011</v>
+        <v>537030</v>
       </c>
       <c r="R9" t="n">
-        <v>6439483</v>
+        <v>6439597</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,40 +1553,34 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120379560</v>
+        <v>120390040</v>
       </c>
       <c r="B10" t="n">
-        <v>100194</v>
+        <v>87348</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,34 +1593,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>4377</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blodvaxskivling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537001</v>
+        <v>537043</v>
       </c>
       <c r="R10" t="n">
-        <v>6439528</v>
+        <v>6439682</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,28 +1672,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120379556</v>
+        <v>120375394</v>
       </c>
       <c r="B11" t="n">
-        <v>74593</v>
+        <v>91881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,38 +1703,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537015</v>
+        <v>537091</v>
       </c>
       <c r="R11" t="n">
-        <v>6439520</v>
+        <v>6439460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,9 +1764,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,22 +1791,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120376327</v>
+        <v>120379558</v>
       </c>
       <c r="B12" t="n">
-        <v>8421</v>
+        <v>89981</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,21 +1819,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>5685</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1819,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536994</v>
+        <v>537031</v>
       </c>
       <c r="R12" t="n">
-        <v>6439456</v>
+        <v>6439570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,19 +1876,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1879,22 +1893,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Jon Liljebäck, Gunilla Rech</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120390059</v>
+        <v>120379556</v>
       </c>
       <c r="B13" t="n">
-        <v>108811</v>
+        <v>74593</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,42 +1917,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537051</v>
+        <v>537015</v>
       </c>
       <c r="R13" t="n">
-        <v>6439570</v>
+        <v>6439520</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,29 +1989,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120379559</v>
+        <v>120374719</v>
       </c>
       <c r="B14" t="n">
-        <v>94422</v>
+        <v>91881</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,38 +2019,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2671</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537007</v>
+        <v>537088</v>
       </c>
       <c r="R14" t="n">
-        <v>6439489</v>
+        <v>6439432</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2088,12 +2097,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2202,10 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120390295</v>
+        <v>120375204</v>
       </c>
       <c r="B16" t="n">
-        <v>4772</v>
+        <v>91881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,47 +2223,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537052</v>
+        <v>537127</v>
       </c>
       <c r="R16" t="n">
-        <v>6439544</v>
+        <v>6439407</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,40 +2289,34 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>vid basen av brant</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120386440</v>
+        <v>120376327</v>
       </c>
       <c r="B17" t="n">
-        <v>100194</v>
+        <v>8421</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2335,21 +2329,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2359,10 +2353,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537030</v>
+        <v>536994</v>
       </c>
       <c r="R17" t="n">
-        <v>6439597</v>
+        <v>6439456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,9 +2386,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,22 +2413,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120375394</v>
+        <v>120379933</v>
       </c>
       <c r="B18" t="n">
-        <v>91881</v>
+        <v>5169</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2433,38 +2437,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537091</v>
+        <v>537011</v>
       </c>
       <c r="R18" t="n">
-        <v>6439460</v>
+        <v>6439483</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,19 +2515,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:31</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2515,25 +2531,26 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120374719</v>
+        <v>120375781</v>
       </c>
       <c r="B19" t="n">
         <v>91881</v>
@@ -2573,10 +2590,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537088</v>
+        <v>537122</v>
       </c>
       <c r="R19" t="n">
-        <v>6439432</v>
+        <v>6439387</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,22 +2640,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120390305</v>
+        <v>120379559</v>
       </c>
       <c r="B20" t="n">
-        <v>5169</v>
+        <v>94422</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2651,43 +2668,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>2671</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537033</v>
+        <v>537007</v>
       </c>
       <c r="R20" t="n">
-        <v>6439525</v>
+        <v>6439489</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,26 +2736,25 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120375781</v>
+        <v>120375071</v>
       </c>
       <c r="B21" t="n">
         <v>91881</v>
@@ -2787,10 +2794,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537122</v>
+        <v>537126</v>
       </c>
       <c r="R21" t="n">
-        <v>6439387</v>
+        <v>6439407</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,22 +2844,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120375071</v>
+        <v>120390059</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>108811</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2865,34 +2872,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537126</v>
+        <v>537051</v>
       </c>
       <c r="R22" t="n">
-        <v>6439407</v>
+        <v>6439570</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2933,28 +2944,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120390040</v>
+        <v>120377550</v>
       </c>
       <c r="B23" t="n">
-        <v>87348</v>
+        <v>91881</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2963,49 +2975,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4377</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537043</v>
+        <v>537101</v>
       </c>
       <c r="R23" t="n">
-        <v>6439682</v>
+        <v>6439502</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3035,40 +3036,49 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120374873</v>
+        <v>120379555</v>
       </c>
       <c r="B24" t="n">
-        <v>91901</v>
+        <v>74466</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3077,52 +3087,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5448</v>
+        <v>6428</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537033</v>
+        <v>537027</v>
       </c>
       <c r="R24" t="n">
-        <v>6439605</v>
+        <v>6439571</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3152,54 +3151,55 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gran blandskog</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120375204</v>
+        <v>120390305</v>
       </c>
       <c r="B25" t="n">
-        <v>91881</v>
+        <v>5169</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3208,38 +3208,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537127</v>
+        <v>537033</v>
       </c>
       <c r="R25" t="n">
-        <v>6439407</v>
+        <v>6439525</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3280,28 +3289,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120374870</v>
+        <v>120376738</v>
       </c>
       <c r="B26" t="n">
-        <v>91881</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3314,31 +3324,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Svartgölen, Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537094</v>
+        <v>537025</v>
       </c>
       <c r="R26" t="n">
         <v>6439477</v>
@@ -3371,19 +3381,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,12 +3398,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120379555</v>
+        <v>120376738</v>
       </c>
       <c r="B24" t="n">
-        <v>74466</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3087,41 +3087,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Svartgölen, Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537027</v>
+        <v>537025</v>
       </c>
       <c r="R24" t="n">
-        <v>6439571</v>
+        <v>6439477</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3162,44 +3159,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120390305</v>
+        <v>120379555</v>
       </c>
       <c r="B25" t="n">
-        <v>5169</v>
+        <v>74466</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3212,43 +3193,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>6428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537033</v>
+        <v>537027</v>
       </c>
       <c r="R25" t="n">
-        <v>6439525</v>
+        <v>6439571</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3293,25 +3268,40 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120376738</v>
+        <v>120390305</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3320,38 +3310,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537025</v>
+        <v>537033</v>
       </c>
       <c r="R26" t="n">
-        <v>6439477</v>
+        <v>6439525</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,18 +3391,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120374873</v>
+        <v>120389940</v>
       </c>
       <c r="B2" t="n">
         <v>91901</v>
@@ -715,24 +715,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537033</v>
+        <v>537043</v>
       </c>
       <c r="R2" t="n">
-        <v>6439605</v>
+        <v>6439607</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,24 +759,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gran blandskog</t>
+          <t>under gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,25 +775,26 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120374870</v>
+        <v>120375394</v>
       </c>
       <c r="B3" t="n">
         <v>91881</v>
@@ -842,14 +830,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537094</v>
+        <v>537091</v>
       </c>
       <c r="R3" t="n">
-        <v>6439477</v>
+        <v>6439460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +894,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120390295</v>
+        <v>120379555</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>74466</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,43 +922,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537052</v>
+        <v>537027</v>
       </c>
       <c r="R4" t="n">
-        <v>6439544</v>
+        <v>6439571</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,11 +987,6 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>vid basen av brant</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1020,25 +997,40 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120390290</v>
+        <v>120374719</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,47 +1039,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537047</v>
+        <v>537088</v>
       </c>
       <c r="R5" t="n">
-        <v>6439540</v>
+        <v>6439432</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,40 +1105,34 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>gammal gran i brant sluttning</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120379560</v>
+        <v>120375071</v>
       </c>
       <c r="B6" t="n">
-        <v>100194</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,38 +1141,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537001</v>
+        <v>537126</v>
       </c>
       <c r="R6" t="n">
-        <v>6439528</v>
+        <v>6439407</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,22 +1219,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120386436</v>
+        <v>120377550</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,38 +1243,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537025</v>
+        <v>537101</v>
       </c>
       <c r="R7" t="n">
-        <v>6439508</v>
+        <v>6439502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,9 +1304,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,22 +1331,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120389940</v>
+        <v>120375204</v>
       </c>
       <c r="B8" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,45 +1359,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537043</v>
+        <v>537127</v>
       </c>
       <c r="R8" t="n">
-        <v>6439607</v>
+        <v>6439407</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,37 +1421,31 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>under gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120386440</v>
+        <v>120379560</v>
       </c>
       <c r="B9" t="n">
         <v>100194</v>
@@ -1515,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537030</v>
+        <v>537001</v>
       </c>
       <c r="R9" t="n">
-        <v>6439597</v>
+        <v>6439528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,22 +1535,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120390040</v>
+        <v>120375781</v>
       </c>
       <c r="B10" t="n">
-        <v>87348</v>
+        <v>91881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,49 +1559,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4377</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537043</v>
+        <v>537122</v>
       </c>
       <c r="R10" t="n">
-        <v>6439682</v>
+        <v>6439387</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,29 +1631,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120375394</v>
+        <v>120390295</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>4772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,38 +1661,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537091</v>
+        <v>537052</v>
       </c>
       <c r="R11" t="n">
-        <v>6439460</v>
+        <v>6439544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1764,19 +1731,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:31</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>vid basen av brant</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,28 +1747,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120379558</v>
+        <v>120374870</v>
       </c>
       <c r="B12" t="n">
-        <v>89981</v>
+        <v>91881</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,38 +1778,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5685</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537031</v>
+        <v>537094</v>
       </c>
       <c r="R12" t="n">
-        <v>6439570</v>
+        <v>6439477</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,9 +1839,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,22 +1866,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Gunilla Rech</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120379556</v>
+        <v>120386436</v>
       </c>
       <c r="B13" t="n">
-        <v>74593</v>
+        <v>4772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1921,21 +1894,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1945,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537015</v>
+        <v>537025</v>
       </c>
       <c r="R13" t="n">
-        <v>6439520</v>
+        <v>6439508</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,22 +1968,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120374719</v>
+        <v>120379561</v>
       </c>
       <c r="B14" t="n">
-        <v>91881</v>
+        <v>100194</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,38 +1992,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537088</v>
+        <v>537004</v>
       </c>
       <c r="R14" t="n">
-        <v>6439432</v>
+        <v>6439579</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,22 +2070,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120379561</v>
+        <v>120374873</v>
       </c>
       <c r="B15" t="n">
-        <v>100194</v>
+        <v>91901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,38 +2094,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>5448</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537004</v>
+        <v>537033</v>
       </c>
       <c r="R15" t="n">
-        <v>6439579</v>
+        <v>6439605</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2182,9 +2169,24 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gran blandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,22 +2201,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120375204</v>
+        <v>120379933</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>5169</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2223,38 +2225,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537127</v>
+        <v>537011</v>
       </c>
       <c r="R16" t="n">
-        <v>6439407</v>
+        <v>6439483</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,34 +2308,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120376327</v>
+        <v>120386440</v>
       </c>
       <c r="B17" t="n">
-        <v>8421</v>
+        <v>100194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2329,21 +2354,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2353,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536994</v>
+        <v>537030</v>
       </c>
       <c r="R17" t="n">
-        <v>6439456</v>
+        <v>6439597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,19 +2411,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,22 +2428,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120379933</v>
+        <v>120379558</v>
       </c>
       <c r="B18" t="n">
-        <v>5169</v>
+        <v>89981</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2441,51 +2456,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>5685</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537011</v>
+        <v>537031</v>
       </c>
       <c r="R18" t="n">
-        <v>6439483</v>
+        <v>6439570</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,40 +2518,34 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Jon Liljebäck, Gunilla Rech</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120375781</v>
+        <v>120379556</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>74593</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2562,38 +2554,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537122</v>
+        <v>537015</v>
       </c>
       <c r="R19" t="n">
-        <v>6439387</v>
+        <v>6439520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,22 +2632,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120379559</v>
+        <v>120390305</v>
       </c>
       <c r="B20" t="n">
-        <v>94422</v>
+        <v>5169</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2668,34 +2660,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2671</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537007</v>
+        <v>537033</v>
       </c>
       <c r="R20" t="n">
-        <v>6439489</v>
+        <v>6439525</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,28 +2737,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120375071</v>
+        <v>120379559</v>
       </c>
       <c r="B21" t="n">
-        <v>91881</v>
+        <v>94422</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2766,38 +2768,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>2671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537126</v>
+        <v>537007</v>
       </c>
       <c r="R21" t="n">
-        <v>6439407</v>
+        <v>6439489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2844,12 +2846,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2963,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120377550</v>
+        <v>120390290</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
+        <v>4772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2975,38 +2977,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537101</v>
+        <v>537047</v>
       </c>
       <c r="R23" t="n">
-        <v>6439502</v>
+        <v>6439540</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,19 +3047,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:08</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>gammal gran i brant sluttning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,28 +3063,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120376738</v>
+        <v>120376327</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>8421</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3087,38 +3094,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537025</v>
+        <v>536994</v>
       </c>
       <c r="R24" t="n">
-        <v>6439477</v>
+        <v>6439456</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3148,9 +3155,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3165,22 +3182,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120379555</v>
+        <v>120390040</v>
       </c>
       <c r="B25" t="n">
-        <v>74466</v>
+        <v>87348</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3193,37 +3210,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6428</v>
+        <v>4377</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blodvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537027</v>
+        <v>537043</v>
       </c>
       <c r="R25" t="n">
-        <v>6439571</v>
+        <v>6439682</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3268,40 +3293,25 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120390305</v>
+        <v>120376738</v>
       </c>
       <c r="B26" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3310,47 +3320,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537033</v>
+        <v>537025</v>
       </c>
       <c r="R26" t="n">
-        <v>6439525</v>
+        <v>6439477</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3391,26 +3392,25 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120411281</v>
+        <v>120411279</v>
       </c>
       <c r="B27" t="n">
         <v>91881</v>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537105</v>
+        <v>537083</v>
       </c>
       <c r="R27" t="n">
-        <v>6439457</v>
+        <v>6439499</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,6 +3486,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,7 +3517,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120411279</v>
+        <v>120411281</v>
       </c>
       <c r="B28" t="n">
         <v>91881</v>
@@ -3552,10 +3557,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537083</v>
+        <v>537105</v>
       </c>
       <c r="R28" t="n">
-        <v>6439499</v>
+        <v>6439457</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,11 +3593,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120389940</v>
+        <v>120379561</v>
       </c>
       <c r="B2" t="n">
-        <v>91901</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537043</v>
+        <v>537004</v>
       </c>
       <c r="R2" t="n">
-        <v>6439607</v>
+        <v>6439579</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,37 +753,31 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>under gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120375394</v>
+        <v>120374870</v>
       </c>
       <c r="B3" t="n">
         <v>91881</v>
@@ -830,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537091</v>
+        <v>537094</v>
       </c>
       <c r="R3" t="n">
-        <v>6439460</v>
+        <v>6439477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120379555</v>
+        <v>120386440</v>
       </c>
       <c r="B4" t="n">
-        <v>74466</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,37 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537027</v>
+        <v>537030</v>
       </c>
       <c r="R4" t="n">
-        <v>6439571</v>
+        <v>6439597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,44 +973,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120374719</v>
+        <v>120376738</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Svartgölen, Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537088</v>
+        <v>537025</v>
       </c>
       <c r="R5" t="n">
-        <v>6439432</v>
+        <v>6439477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120375071</v>
+        <v>120389940</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91901</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,34 +1109,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537126</v>
+        <v>537043</v>
       </c>
       <c r="R6" t="n">
-        <v>6439407</v>
+        <v>6439607</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,34 +1182,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>under gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120377550</v>
+        <v>120390040</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>87348</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,38 +1224,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4377</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blodvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537101</v>
+        <v>537043</v>
       </c>
       <c r="R7" t="n">
-        <v>6439502</v>
+        <v>6439682</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,46 +1296,37 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120375204</v>
+        <v>120375071</v>
       </c>
       <c r="B8" t="n">
         <v>91881</v>
@@ -1383,7 +1366,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537127</v>
+        <v>537126</v>
       </c>
       <c r="R8" t="n">
         <v>6439407</v>
@@ -1445,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120379560</v>
+        <v>120386436</v>
       </c>
       <c r="B9" t="n">
-        <v>100194</v>
+        <v>4772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537001</v>
+        <v>537025</v>
       </c>
       <c r="R9" t="n">
-        <v>6439528</v>
+        <v>6439508</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,22 +1518,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Ulf Fransson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120375781</v>
+        <v>120379558</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>89981</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,38 +1542,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jättegryta, Jättegryta, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537122</v>
+        <v>537031</v>
       </c>
       <c r="R10" t="n">
-        <v>6439387</v>
+        <v>6439570</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,22 +1620,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Nilsson</t>
+          <t>Jon Liljebäck, Gunilla Rech</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120390295</v>
+        <v>120375204</v>
       </c>
       <c r="B11" t="n">
-        <v>4772</v>
+        <v>91881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,47 +1644,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537052</v>
+        <v>537127</v>
       </c>
       <c r="R11" t="n">
-        <v>6439544</v>
+        <v>6439407</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,40 +1710,34 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>vid basen av brant</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120374870</v>
+        <v>120376327</v>
       </c>
       <c r="B12" t="n">
-        <v>91881</v>
+        <v>8421</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,38 +1746,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537094</v>
+        <v>536994</v>
       </c>
       <c r="R12" t="n">
-        <v>6439477</v>
+        <v>6439456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1809,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1819,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,22 +1834,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120386436</v>
+        <v>120374873</v>
       </c>
       <c r="B13" t="n">
-        <v>4772</v>
+        <v>91901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,38 +1858,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537025</v>
+        <v>537033</v>
       </c>
       <c r="R13" t="n">
-        <v>6439508</v>
+        <v>6439605</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,9 +1933,24 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gran blandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,22 +1965,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120379561</v>
+        <v>120390290</v>
       </c>
       <c r="B14" t="n">
-        <v>100194</v>
+        <v>4772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,34 +1993,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537004</v>
+        <v>537047</v>
       </c>
       <c r="R14" t="n">
-        <v>6439579</v>
+        <v>6439540</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,34 +2064,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>gammal gran i brant sluttning</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120374873</v>
+        <v>120390059</v>
       </c>
       <c r="B15" t="n">
-        <v>91901</v>
+        <v>108811</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,48 +2110,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5448</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537033</v>
+        <v>537051</v>
       </c>
       <c r="R15" t="n">
-        <v>6439605</v>
+        <v>6439570</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,54 +2171,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gran blandskog</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120379933</v>
+        <v>120379559</v>
       </c>
       <c r="B16" t="n">
-        <v>5169</v>
+        <v>94422</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2229,51 +2217,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>2671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537011</v>
+        <v>537007</v>
       </c>
       <c r="R16" t="n">
-        <v>6439483</v>
+        <v>6439489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,40 +2279,34 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michael Söderström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120386440</v>
+        <v>120375781</v>
       </c>
       <c r="B17" t="n">
-        <v>100194</v>
+        <v>91881</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2350,38 +2315,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537030</v>
+        <v>537122</v>
       </c>
       <c r="R17" t="n">
-        <v>6439597</v>
+        <v>6439387</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,22 +2393,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulf Fransson</t>
+          <t>Linnea Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120379558</v>
+        <v>120375394</v>
       </c>
       <c r="B18" t="n">
-        <v>89981</v>
+        <v>91881</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2452,38 +2417,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5685</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537031</v>
+        <v>537091</v>
       </c>
       <c r="R18" t="n">
-        <v>6439570</v>
+        <v>6439460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,9 +2478,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,22 +2505,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Gunilla Rech</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120379556</v>
+        <v>120374719</v>
       </c>
       <c r="B19" t="n">
-        <v>74593</v>
+        <v>91881</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2554,38 +2529,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Jättegryta, Jättegryta, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537015</v>
+        <v>537088</v>
       </c>
       <c r="R19" t="n">
-        <v>6439520</v>
+        <v>6439432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,22 +2607,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120390305</v>
+        <v>120377550</v>
       </c>
       <c r="B20" t="n">
-        <v>5169</v>
+        <v>91881</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,47 +2631,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537033</v>
+        <v>537101</v>
       </c>
       <c r="R20" t="n">
-        <v>6439525</v>
+        <v>6439502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2726,40 +2692,49 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120379559</v>
+        <v>120379555</v>
       </c>
       <c r="B21" t="n">
-        <v>94422</v>
+        <v>74466</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,34 +2747,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2671</v>
+        <v>6428</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537007</v>
+        <v>537027</v>
       </c>
       <c r="R21" t="n">
-        <v>6439489</v>
+        <v>6439571</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,8 +2818,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2858,10 +2852,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120390059</v>
+        <v>120390305</v>
       </c>
       <c r="B22" t="n">
-        <v>108811</v>
+        <v>5169</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,31 +2864,36 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2902,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537051</v>
+        <v>537033</v>
       </c>
       <c r="R22" t="n">
-        <v>6439570</v>
+        <v>6439525</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2965,10 +2964,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120390290</v>
+        <v>120379560</v>
       </c>
       <c r="B23" t="n">
-        <v>4772</v>
+        <v>100194</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2981,43 +2980,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537047</v>
+        <v>537001</v>
       </c>
       <c r="R23" t="n">
-        <v>6439540</v>
+        <v>6439528</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3052,40 +3042,34 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>gammal gran i brant sluttning</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120376327</v>
+        <v>120379556</v>
       </c>
       <c r="B24" t="n">
-        <v>8421</v>
+        <v>74593</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3098,21 +3082,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3122,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536994</v>
+        <v>537015</v>
       </c>
       <c r="R24" t="n">
-        <v>6439456</v>
+        <v>6439520</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3155,19 +3139,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3182,22 +3156,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120390040</v>
+        <v>120390295</v>
       </c>
       <c r="B25" t="n">
-        <v>87348</v>
+        <v>4772</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3210,34 +3184,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4377</v>
+        <v>102306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3245,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537043</v>
+        <v>537052</v>
       </c>
       <c r="R25" t="n">
-        <v>6439682</v>
+        <v>6439544</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3281,6 +3253,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>vid basen av brant</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,10 +3285,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120376738</v>
+        <v>120379933</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>5169</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3320,38 +3297,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Ög</t>
+          <t>Öst Svartgölen, Väsby branter NR, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537025</v>
+        <v>537011</v>
       </c>
       <c r="R26" t="n">
-        <v>6439477</v>
+        <v>6439483</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3386,31 +3380,37 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På lutande grantorraka, c:a 125 meter SO Svartgölens sydspets.Alldeles utanför reservatsgränsen.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Michael Söderström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120411279</v>
+        <v>120411281</v>
       </c>
       <c r="B27" t="n">
         <v>91881</v>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537083</v>
+        <v>537105</v>
       </c>
       <c r="R27" t="n">
-        <v>6439499</v>
+        <v>6439457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,11 +3486,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3517,7 +3512,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120411281</v>
+        <v>120411279</v>
       </c>
       <c r="B28" t="n">
         <v>91881</v>
@@ -3557,10 +3552,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537105</v>
+        <v>537083</v>
       </c>
       <c r="R28" t="n">
-        <v>6439457</v>
+        <v>6439499</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3593,6 +3588,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120377550</v>
+        <v>120379555</v>
       </c>
       <c r="B20" t="n">
-        <v>91881</v>
+        <v>74466</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,38 +2631,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>6428</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kättilkullen, Kättilkullen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537101</v>
+        <v>537027</v>
       </c>
       <c r="R20" t="n">
-        <v>6439502</v>
+        <v>6439571</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,49 +2695,55 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120379555</v>
+        <v>120377550</v>
       </c>
       <c r="B21" t="n">
-        <v>74466</v>
+        <v>91881</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2743,41 +2752,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6428</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Kättilkullen, Kättilkullen, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537027</v>
+        <v>537101</v>
       </c>
       <c r="R21" t="n">
-        <v>6439571</v>
+        <v>6439502</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,45 +2813,39 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120379556</v>
+        <v>120390295</v>
       </c>
       <c r="B24" t="n">
-        <v>74593</v>
+        <v>4772</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3082,34 +3082,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartgölen, Ög</t>
+          <t>Ost Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537015</v>
+        <v>537052</v>
       </c>
       <c r="R24" t="n">
-        <v>6439520</v>
+        <v>6439544</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,34 +3153,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>vid basen av brant</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120390295</v>
+        <v>120379556</v>
       </c>
       <c r="B25" t="n">
-        <v>4772</v>
+        <v>74593</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3184,43 +3199,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ost Svartgölen, Ög</t>
+          <t>Svartgölen, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537052</v>
+        <v>537015</v>
       </c>
       <c r="R25" t="n">
-        <v>6439544</v>
+        <v>6439520</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,30 +3261,24 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>vid basen av brant</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -1334,7 +1334,7 @@
         <v>121264537</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>121125095</v>
       </c>
       <c r="B30" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -1334,7 +1334,7 @@
         <v>121264537</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>121125095</v>
       </c>
       <c r="B30" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -1334,7 +1334,7 @@
         <v>121264537</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -1334,7 +1334,7 @@
         <v>121264537</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>121125095</v>
       </c>
       <c r="B30" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -1334,7 +1334,7 @@
         <v>121264537</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 25171-2024 artfynd.xlsx
+++ b/artfynd/A 25171-2024 artfynd.xlsx
@@ -1334,7 +1334,7 @@
         <v>121264537</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
